--- a/data/sports/valorant/research.xlsx
+++ b/data/sports/valorant/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ158" headerRowCount="1">
-  <autoFilter ref="A1:DQ158"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ159" headerRowCount="1">
+  <autoFilter ref="A1:DQ159"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$158)</f>
+        <f>COUNTA('Picks'!$A$2:$A$159)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$158,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$159,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$158,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$159,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"win")+COUNTIFS('Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")+COUNTIFS('Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$158,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$159,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$158,"&gt;0",'Picks'!$V$2:$V$158,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$158,"&gt;0",'Picks'!$V$2:$V$158,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$158,"&gt;0",'Picks'!$V$2:$V$158,"win")/(COUNTIFS('Picks'!$BX$2:$BX$158,"&gt;0",'Picks'!$V$2:$V$158,"win")+COUNTIFS('Picks'!$BX$2:$BX$158,"&gt;0",'Picks'!$V$2:$V$158,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")/(COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")+COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$158)/SUM('Picks'!$BX$2:$BX$158),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$159)/SUM('Picks'!$BX$2:$BX$159),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$158)</f>
+        <f>SUM('Picks'!$BY$2:$BY$159)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$158,"&lt;&gt;",'Picks'!$AB$2:$AB$158),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$159,"&lt;&gt;",'Picks'!$AB$2:$AB$159),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$158,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$158,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$159,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$159,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$158,'Picks'!$AM$2:$AM$158,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$159,'Picks'!$AM$2:$AM$159,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A14,'Picks'!$U$2:$U$158,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A14,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A14,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$158,'Picks'!$H$2:$H$158,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$158,'Picks'!$H$2:$H$158,$A14,'Picks'!$U$2:$U$158,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A15,'Picks'!$U$2:$U$158,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A15,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A15,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$158,'Picks'!$H$2:$H$158,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$158,'Picks'!$H$2:$H$158,$A15,'Picks'!$U$2:$U$158,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A16,'Picks'!$U$2:$U$158,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A16,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$158,$A16,'Picks'!$U$2:$U$158,"settled",'Picks'!$V$2:$V$158,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$158,'Picks'!$H$2:$H$158,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$158,'Picks'!$H$2:$H$158,$A16,'Picks'!$U$2:$U$158,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ158"/>
+  <dimension ref="A1:DQ159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52066,6 +52066,303 @@
         </is>
       </c>
     </row>
+    <row r="159" ht="36" customHeight="1">
+      <c r="A159" s="24" t="inlineStr">
+        <is>
+          <t>d979a2a4efd74a1a</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:36.008787Z</t>
+        </is>
+      </c>
+      <c r="C159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D159" s="24" t="inlineStr">
+        <is>
+          <t>142716</t>
+        </is>
+      </c>
+      <c r="E159" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F159" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G159" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="H159" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I159" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J159" s="25" t="n"/>
+      <c r="K159" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L159" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M159" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N159" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O159" s="28" t="n">
+        <v>0.507845</v>
+      </c>
+      <c r="P159" s="28" t="n"/>
+      <c r="Q159" s="28" t="n">
+        <v>-0.031326</v>
+      </c>
+      <c r="R159" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S159" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T159" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U159" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V159" s="24" t="n"/>
+      <c r="W159" s="26" t="n"/>
+      <c r="X159" s="26" t="n"/>
+      <c r="Y159" s="25" t="n"/>
+      <c r="Z159" s="26" t="n"/>
+      <c r="AA159" s="28" t="n"/>
+      <c r="AB159" s="28" t="n"/>
+      <c r="AC159" s="30" t="n"/>
+      <c r="AD159" s="24" t="n"/>
+      <c r="AE159" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-pr-loud-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF159" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG159" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH159" s="24" t="n"/>
+      <c r="AI159" s="31" t="n"/>
+      <c r="AJ159" s="31" t="n"/>
+      <c r="AK159" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL159" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM159" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN159" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO159" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP159" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ159" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR159" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS159" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AT159" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AU159" s="24" t="inlineStr">
+        <is>
+          <t>Paper Rex</t>
+        </is>
+      </c>
+      <c r="AV159" s="24" t="n"/>
+      <c r="AW159" s="24" t="n"/>
+      <c r="AX159" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY159" s="24" t="n"/>
+      <c r="AZ159" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA159" s="24" t="inlineStr">
+        <is>
+          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+        </is>
+      </c>
+      <c r="BB159" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC159" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD159" s="24" t="inlineStr">
+        <is>
+          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+        </is>
+      </c>
+      <c r="BE159" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF159" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG159" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:35.888567Z</t>
+        </is>
+      </c>
+      <c r="BI159" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ159" s="25" t="n"/>
+      <c r="BK159" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL159" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM159" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN159" s="28" t="n"/>
+      <c r="BO159" s="28" t="n"/>
+      <c r="BP159" s="25" t="n"/>
+      <c r="BQ159" s="27" t="n"/>
+      <c r="BR159" s="28" t="n"/>
+      <c r="BS159" s="28" t="n"/>
+      <c r="BT159" s="28" t="n"/>
+      <c r="BU159" s="25" t="n"/>
+      <c r="BV159" s="29" t="n"/>
+      <c r="BW159" s="24" t="n"/>
+      <c r="BX159" s="30" t="n"/>
+      <c r="BY159" s="27" t="n"/>
+      <c r="BZ159" s="24" t="n"/>
+      <c r="CA159" s="31" t="n"/>
+      <c r="CB159" s="24" t="n"/>
+      <c r="CC159" s="24" t="n"/>
+      <c r="CD159" s="24" t="n"/>
+      <c r="CE159" s="24" t="n"/>
+      <c r="CF159" s="24" t="n"/>
+      <c r="CG159" s="24" t="n"/>
+      <c r="CH159" s="24" t="n"/>
+      <c r="CI159" s="24" t="n"/>
+      <c r="CJ159" s="24" t="n"/>
+      <c r="CK159" s="24" t="n"/>
+      <c r="CL159" s="24" t="n"/>
+      <c r="CM159" s="24" t="n"/>
+      <c r="CN159" s="24" t="n"/>
+      <c r="CO159" s="24" t="n"/>
+      <c r="CP159" s="24" t="n"/>
+      <c r="CQ159" s="24" t="n"/>
+      <c r="CR159" s="24" t="n"/>
+      <c r="CS159" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT159" s="24" t="n"/>
+      <c r="CU159" s="24" t="n"/>
+      <c r="CV159" s="24" t="n"/>
+      <c r="CW159" s="24" t="n"/>
+      <c r="CX159" s="24" t="n"/>
+      <c r="CY159" s="24" t="n"/>
+      <c r="CZ159" s="24" t="n"/>
+      <c r="DA159" s="24" t="n"/>
+      <c r="DB159" s="24" t="n"/>
+      <c r="DC159" s="24" t="n"/>
+      <c r="DD159" s="24" t="n"/>
+      <c r="DE159" s="24" t="n"/>
+      <c r="DF159" s="24" t="n"/>
+      <c r="DG159" s="24" t="n"/>
+      <c r="DH159" s="24" t="n"/>
+      <c r="DI159" s="24" t="n"/>
+      <c r="DJ159" s="24" t="n"/>
+      <c r="DK159" s="24" t="n"/>
+      <c r="DL159" s="24" t="n"/>
+      <c r="DM159" s="24" t="n"/>
+      <c r="DN159" s="24" t="n"/>
+      <c r="DO159" s="24" t="n"/>
+      <c r="DP159" s="24" t="n"/>
+      <c r="DQ159" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0", "away_team": "LOUD", "event_id": "142716", "event_start_utc": "2026-10-07T12:00:00Z", "features": {"away_elo": 1889.097652, "away_history_count": 91, "home_elo": 1888.453929, "home_history_count": 166}, "historical_source_observation_times_verified": false, "home_team": "Paper Rex", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6874": 91, "bo3:2:7225": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6874": "2026-10-04T09:00:00Z", "bo3:2:7225": "2026-09-29T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11337757343423142, "platt_slope": 0.7693916714547524, "ratings": {"bo3:2:6874": 1889.097652, "bo3:2:7225": 1888.453929}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.579410+00:00", "team_ids": ["bo3:2:7225", "bo3:2:6874"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.579410+00:00", "probabilities": {"away": 0.492155, "home": 0.507845}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "c8df0978f4919f2c9dc642e981f2db5ff78d418f15e34787b0a5bcc999e56a05", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/valorant/research.xlsx
+++ b/data/sports/valorant/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ159" headerRowCount="1">
-  <autoFilter ref="A1:DQ159"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ165" headerRowCount="1">
+  <autoFilter ref="A1:DQ165"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$159)</f>
+        <f>COUNTA('Picks'!$A$2:$A$165)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$159,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$165,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$159,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$165,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")+COUNTIFS('Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"win")+COUNTIFS('Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$159,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$165,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$165,"&gt;0",'Picks'!$V$2:$V$165,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$165,"&gt;0",'Picks'!$V$2:$V$165,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")/(COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"win")+COUNTIFS('Picks'!$BX$2:$BX$159,"&gt;0",'Picks'!$V$2:$V$159,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$165,"&gt;0",'Picks'!$V$2:$V$165,"win")/(COUNTIFS('Picks'!$BX$2:$BX$165,"&gt;0",'Picks'!$V$2:$V$165,"win")+COUNTIFS('Picks'!$BX$2:$BX$165,"&gt;0",'Picks'!$V$2:$V$165,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$159)/SUM('Picks'!$BX$2:$BX$159),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$165)/SUM('Picks'!$BX$2:$BX$165),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$159)</f>
+        <f>SUM('Picks'!$BY$2:$BY$165)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$159,"&lt;&gt;",'Picks'!$AB$2:$AB$159),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$165,"&lt;&gt;",'Picks'!$AB$2:$AB$165),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$159,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$159,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$165,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$165,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$159,'Picks'!$AM$2:$AM$159,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$165,'Picks'!$AM$2:$AM$165,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A14,'Picks'!$U$2:$U$165,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A14,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A14,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$165,'Picks'!$H$2:$H$165,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A14,'Picks'!$U$2:$U$159,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$165,'Picks'!$H$2:$H$165,$A14,'Picks'!$U$2:$U$165,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A15,'Picks'!$U$2:$U$165,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A15,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A15,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$165,'Picks'!$H$2:$H$165,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A15,'Picks'!$U$2:$U$159,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$165,'Picks'!$H$2:$H$165,$A15,'Picks'!$U$2:$U$165,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A16,'Picks'!$U$2:$U$165,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A16,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled",'Picks'!$V$2:$V$159,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$165,$A16,'Picks'!$U$2:$U$165,"settled",'Picks'!$V$2:$V$165,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$159,'Picks'!$H$2:$H$159,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$165,'Picks'!$H$2:$H$165,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$159,'Picks'!$H$2:$H$159,$A16,'Picks'!$U$2:$U$159,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$165,'Picks'!$H$2:$H$165,$A16,'Picks'!$U$2:$U$165,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ159"/>
+  <dimension ref="A1:DQ165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52069,22 +52069,22 @@
     <row r="159" ht="36" customHeight="1">
       <c r="A159" s="24" t="inlineStr">
         <is>
-          <t>d979a2a4efd74a1a</t>
+          <t>1b0fa9f2a0b1491c</t>
         </is>
       </c>
       <c r="B159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:36.008787Z</t>
+          <t>2026-10-07T22:28:03.285581Z</t>
         </is>
       </c>
       <c r="C159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-07T12:00:00Z</t>
+          <t>2026-10-08T09:00:00Z</t>
         </is>
       </c>
       <c r="D159" s="24" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>143386</t>
         </is>
       </c>
       <c r="E159" s="24" t="inlineStr">
@@ -52094,12 +52094,12 @@
       </c>
       <c r="F159" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="G159" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="H159" s="24" t="inlineStr">
@@ -52119,23 +52119,23 @@
         </is>
       </c>
       <c r="L159" s="26" t="n">
-        <v>-117</v>
+        <v>-203</v>
       </c>
       <c r="M159" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.492611</v>
       </c>
       <c r="N159" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.669967</v>
       </c>
       <c r="O159" s="28" t="n">
-        <v>0.507845</v>
+        <v>0.723571</v>
       </c>
       <c r="P159" s="28" t="n"/>
       <c r="Q159" s="28" t="n">
-        <v>-0.031326</v>
+        <v>0.053604</v>
       </c>
       <c r="R159" s="26" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="S159" s="29" t="n">
         <v>1</v>
@@ -52147,21 +52147,41 @@
       </c>
       <c r="U159" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V159" s="24" t="n"/>
-      <c r="W159" s="26" t="n"/>
-      <c r="X159" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V159" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W159" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X159" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y159" s="25" t="n"/>
-      <c r="Z159" s="26" t="n"/>
-      <c r="AA159" s="28" t="n"/>
-      <c r="AB159" s="28" t="n"/>
-      <c r="AC159" s="30" t="n"/>
-      <c r="AD159" s="24" t="n"/>
+      <c r="Z159" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA159" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB159" s="28" t="n">
+        <v>-0.019967</v>
+      </c>
+      <c r="AC159" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:15.929870Z</t>
+        </is>
+      </c>
       <c r="AE159" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-pr-loud-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-100t-g2-2026-10-08).</t>
         </is>
       </c>
       <c r="AF159" s="31" t="inlineStr">
@@ -52171,7 +52191,7 @@
       </c>
       <c r="AG159" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH159" s="24" t="n"/>
@@ -52179,7 +52199,7 @@
       <c r="AJ159" s="31" t="n"/>
       <c r="AK159" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL159" s="26" t="n">
@@ -52187,7 +52207,7 @@
       </c>
       <c r="AM159" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN159" s="24" t="inlineStr">
@@ -52197,37 +52217,37 @@
       </c>
       <c r="AO159" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP159" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AQ159" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AR159" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>G2 Esports</t>
         </is>
       </c>
       <c r="AS159" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AT159" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AU159" s="24" t="inlineStr">
         <is>
-          <t>Paper Rex</t>
+          <t>100 Thieves</t>
         </is>
       </c>
       <c r="AV159" s="24" t="n"/>
@@ -52245,7 +52265,7 @@
       </c>
       <c r="BA159" s="24" t="inlineStr">
         <is>
-          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
         </is>
       </c>
       <c r="BB159" s="24" t="inlineStr">
@@ -52260,7 +52280,7 @@
       </c>
       <c r="BD159" s="24" t="inlineStr">
         <is>
-          <t>bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0</t>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
         </is>
       </c>
       <c r="BE159" s="24" t="inlineStr">
@@ -52280,7 +52300,7 @@
       </c>
       <c r="BH159" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:35.888567Z</t>
+          <t>2026-10-07T22:27:21.757131Z</t>
         </is>
       </c>
       <c r="BI159" s="24" t="inlineStr">
@@ -52290,19 +52310,23 @@
       </c>
       <c r="BJ159" s="25" t="n"/>
       <c r="BK159" s="26" t="n">
-        <v>-117</v>
+        <v>-203</v>
       </c>
       <c r="BL159" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.492611</v>
       </c>
       <c r="BM159" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.669967</v>
       </c>
       <c r="BN159" s="28" t="n"/>
       <c r="BO159" s="28" t="n"/>
       <c r="BP159" s="25" t="n"/>
-      <c r="BQ159" s="27" t="n"/>
-      <c r="BR159" s="28" t="n"/>
+      <c r="BQ159" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR159" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS159" s="28" t="n"/>
       <c r="BT159" s="28" t="n"/>
       <c r="BU159" s="25" t="n"/>
@@ -52331,7 +52355,7 @@
       <c r="CR159" s="24" t="n"/>
       <c r="CS159" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT159" s="24" t="n"/>
@@ -52359,7 +52383,1913 @@
       <c r="DP159" s="24" t="n"/>
       <c r="DQ159" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "bc2ff58a28711caad18e6e2fb5c84c5219037c1ef4e051e4784c50b9dd6905e0", "away_team": "LOUD", "event_id": "142716", "event_start_utc": "2026-10-07T12:00:00Z", "features": {"away_elo": 1889.097652, "away_history_count": 91, "home_elo": 1888.453929, "home_history_count": 166}, "historical_source_observation_times_verified": false, "home_team": "Paper Rex", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6874": 91, "bo3:2:7225": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6874": "2026-10-04T09:00:00Z", "bo3:2:7225": "2026-09-29T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11337757343423142, "platt_slope": 0.7693916714547524, "ratings": {"bo3:2:6874": 1889.097652, "bo3:2:7225": 1888.453929}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.579410+00:00", "team_ids": ["bo3:2:7225", "bo3:2:6874"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.579410+00:00", "probabilities": {"away": 0.492155, "home": 0.507845}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "c8df0978f4919f2c9dc642e981f2db5ff78d418f15e34787b0a5bcc999e56a05", "sport": "VALORANT"}</t>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "G2 Esports", "event_id": "143386", "event_start_utc": "2026-10-08T09:00:00Z", "features": {"away_elo": 1871.551684, "away_history_count": 166, "home_elo": 2128.058641, "home_history_count": 111}, "historical_source_observation_times_verified": false, "home_team": "100 Thieves", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7298": 111, "bo3:2:7323": 166}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7298": "2026-09-30T12:00:00Z", "bo3:2:7323": "2026-10-03T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:7298": 2128.058641, "bo3:2:7323": 1871.551684}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7298", "bo3:2:7323"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.276429, "home": 0.723571}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "90d84142df5664be5a6794d40b59aef102d8e86cc1195cd3a358395cbe556e80", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="36" customHeight="1">
+      <c r="A160" s="24" t="inlineStr">
+        <is>
+          <t>2aa9f491c03d4160</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.285581Z</t>
+        </is>
+      </c>
+      <c r="C160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D160" s="24" t="inlineStr">
+        <is>
+          <t>143487</t>
+        </is>
+      </c>
+      <c r="E160" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F160" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="G160" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="H160" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I160" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J160" s="25" t="n"/>
+      <c r="K160" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L160" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M160" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N160" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O160" s="28" t="n">
+        <v>0.539506</v>
+      </c>
+      <c r="P160" s="28" t="n"/>
+      <c r="Q160" s="28" t="n">
+        <v>-0.010044</v>
+      </c>
+      <c r="R160" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="S160" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T160" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U160" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V160" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W160" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y160" s="25" t="n"/>
+      <c r="Z160" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA160" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB160" s="28" t="n">
+        <v>-0.009549999999999999</v>
+      </c>
+      <c r="AC160" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:18.437546Z</t>
+        </is>
+      </c>
+      <c r="AE160" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-vit-ns-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF160" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG160" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH160" s="24" t="n"/>
+      <c r="AI160" s="31" t="n"/>
+      <c r="AJ160" s="31" t="n"/>
+      <c r="AK160" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL160" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM160" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN160" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO160" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP160" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AQ160" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AR160" s="24" t="inlineStr">
+        <is>
+          <t>Nongshim RedForce</t>
+        </is>
+      </c>
+      <c r="AS160" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AT160" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AU160" s="24" t="inlineStr">
+        <is>
+          <t>Team Vitality</t>
+        </is>
+      </c>
+      <c r="AV160" s="24" t="n"/>
+      <c r="AW160" s="24" t="n"/>
+      <c r="AX160" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY160" s="24" t="n"/>
+      <c r="AZ160" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA160" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BB160" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC160" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD160" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BE160" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF160" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG160" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:21.834145Z</t>
+        </is>
+      </c>
+      <c r="BI160" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ160" s="25" t="n"/>
+      <c r="BK160" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL160" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM160" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN160" s="28" t="n"/>
+      <c r="BO160" s="28" t="n"/>
+      <c r="BP160" s="25" t="n"/>
+      <c r="BQ160" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR160" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS160" s="28" t="n"/>
+      <c r="BT160" s="28" t="n"/>
+      <c r="BU160" s="25" t="n"/>
+      <c r="BV160" s="29" t="n"/>
+      <c r="BW160" s="24" t="n"/>
+      <c r="BX160" s="30" t="n"/>
+      <c r="BY160" s="27" t="n"/>
+      <c r="BZ160" s="24" t="n"/>
+      <c r="CA160" s="31" t="n"/>
+      <c r="CB160" s="24" t="n"/>
+      <c r="CC160" s="24" t="n"/>
+      <c r="CD160" s="24" t="n"/>
+      <c r="CE160" s="24" t="n"/>
+      <c r="CF160" s="24" t="n"/>
+      <c r="CG160" s="24" t="n"/>
+      <c r="CH160" s="24" t="n"/>
+      <c r="CI160" s="24" t="n"/>
+      <c r="CJ160" s="24" t="n"/>
+      <c r="CK160" s="24" t="n"/>
+      <c r="CL160" s="24" t="n"/>
+      <c r="CM160" s="24" t="n"/>
+      <c r="CN160" s="24" t="n"/>
+      <c r="CO160" s="24" t="n"/>
+      <c r="CP160" s="24" t="n"/>
+      <c r="CQ160" s="24" t="n"/>
+      <c r="CR160" s="24" t="n"/>
+      <c r="CS160" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT160" s="24" t="n"/>
+      <c r="CU160" s="24" t="n"/>
+      <c r="CV160" s="24" t="n"/>
+      <c r="CW160" s="24" t="n"/>
+      <c r="CX160" s="24" t="n"/>
+      <c r="CY160" s="24" t="n"/>
+      <c r="CZ160" s="24" t="n"/>
+      <c r="DA160" s="24" t="n"/>
+      <c r="DB160" s="24" t="n"/>
+      <c r="DC160" s="24" t="n"/>
+      <c r="DD160" s="24" t="n"/>
+      <c r="DE160" s="24" t="n"/>
+      <c r="DF160" s="24" t="n"/>
+      <c r="DG160" s="24" t="n"/>
+      <c r="DH160" s="24" t="n"/>
+      <c r="DI160" s="24" t="n"/>
+      <c r="DJ160" s="24" t="n"/>
+      <c r="DK160" s="24" t="n"/>
+      <c r="DL160" s="24" t="n"/>
+      <c r="DM160" s="24" t="n"/>
+      <c r="DN160" s="24" t="n"/>
+      <c r="DO160" s="24" t="n"/>
+      <c r="DP160" s="24" t="n"/>
+      <c r="DQ160" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "Nongshim RedForce", "event_id": "143487", "event_start_utc": "2026-10-08T12:00:00Z", "features": {"away_elo": 1937.226353, "away_history_count": 121, "home_elo": 1967.016037, "home_history_count": 105}, "historical_source_observation_times_verified": false, "home_team": "Team Vitality", "inference_inputs": {"book_state": {"games_played": {"bo3:2:6445": 121, "bo3:2:7254": 105}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:6445": "2026-10-03T11:30:00Z", "bo3:2:7254": "2026-09-30T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:6445": 1937.226353, "bo3:2:7254": 1967.016037}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7254", "bo3:2:6445"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.460494, "home": 0.539506}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "23b5ec5a13f99993836831588bfdbe46f7c29410a839491ab1d9d5aabacc5fe7", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="36" customHeight="1">
+      <c r="A161" s="24" t="inlineStr">
+        <is>
+          <t>fc9ee6693727469c</t>
+        </is>
+      </c>
+      <c r="B161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:28:03.285581Z</t>
+        </is>
+      </c>
+      <c r="C161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-08T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D161" s="24" t="inlineStr">
+        <is>
+          <t>143813</t>
+        </is>
+      </c>
+      <c r="E161" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F161" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="G161" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="H161" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I161" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J161" s="25" t="n"/>
+      <c r="K161" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L161" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M161" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N161" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O161" s="28" t="n">
+        <v>0.522617</v>
+      </c>
+      <c r="P161" s="28" t="n"/>
+      <c r="Q161" s="28" t="n">
+        <v>-0.127733</v>
+      </c>
+      <c r="R161" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T161" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U161" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V161" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W161" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y161" s="25" t="n"/>
+      <c r="Z161" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA161" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB161" s="28" t="n">
+        <v>-0.01035</v>
+      </c>
+      <c r="AC161" s="30" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="AD161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T04:37:30.852967Z</t>
+        </is>
+      </c>
+      <c r="AE161" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-valorant-ff-misa-2026-10-08).</t>
+        </is>
+      </c>
+      <c r="AF161" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG161" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH161" s="24" t="n"/>
+      <c r="AI161" s="31" t="n"/>
+      <c r="AJ161" s="31" t="n"/>
+      <c r="AK161" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL161" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM161" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN161" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO161" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP161" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AQ161" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AR161" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AS161" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AT161" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AU161" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AV161" s="24" t="n"/>
+      <c r="AW161" s="24" t="n"/>
+      <c r="AX161" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY161" s="24" t="n"/>
+      <c r="AZ161" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA161" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BB161" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC161" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD161" s="24" t="inlineStr">
+        <is>
+          <t>4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46</t>
+        </is>
+      </c>
+      <c r="BE161" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF161" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG161" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:27:42.222451Z</t>
+        </is>
+      </c>
+      <c r="BI161" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ161" s="25" t="n"/>
+      <c r="BK161" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL161" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM161" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN161" s="28" t="n"/>
+      <c r="BO161" s="28" t="n"/>
+      <c r="BP161" s="25" t="n"/>
+      <c r="BQ161" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR161" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BS161" s="28" t="n"/>
+      <c r="BT161" s="28" t="n"/>
+      <c r="BU161" s="25" t="n"/>
+      <c r="BV161" s="29" t="n"/>
+      <c r="BW161" s="24" t="n"/>
+      <c r="BX161" s="30" t="n"/>
+      <c r="BY161" s="27" t="n"/>
+      <c r="BZ161" s="24" t="n"/>
+      <c r="CA161" s="31" t="n"/>
+      <c r="CB161" s="24" t="n"/>
+      <c r="CC161" s="24" t="n"/>
+      <c r="CD161" s="24" t="n"/>
+      <c r="CE161" s="24" t="n"/>
+      <c r="CF161" s="24" t="n"/>
+      <c r="CG161" s="24" t="n"/>
+      <c r="CH161" s="24" t="n"/>
+      <c r="CI161" s="24" t="n"/>
+      <c r="CJ161" s="24" t="n"/>
+      <c r="CK161" s="24" t="n"/>
+      <c r="CL161" s="24" t="n"/>
+      <c r="CM161" s="24" t="n"/>
+      <c r="CN161" s="24" t="n"/>
+      <c r="CO161" s="24" t="n"/>
+      <c r="CP161" s="24" t="n"/>
+      <c r="CQ161" s="24" t="n"/>
+      <c r="CR161" s="24" t="n"/>
+      <c r="CS161" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT161" s="24" t="n"/>
+      <c r="CU161" s="24" t="n"/>
+      <c r="CV161" s="24" t="n"/>
+      <c r="CW161" s="24" t="n"/>
+      <c r="CX161" s="24" t="n"/>
+      <c r="CY161" s="24" t="n"/>
+      <c r="CZ161" s="24" t="n"/>
+      <c r="DA161" s="24" t="n"/>
+      <c r="DB161" s="24" t="n"/>
+      <c r="DC161" s="24" t="n"/>
+      <c r="DD161" s="24" t="n"/>
+      <c r="DE161" s="24" t="n"/>
+      <c r="DF161" s="24" t="n"/>
+      <c r="DG161" s="24" t="n"/>
+      <c r="DH161" s="24" t="n"/>
+      <c r="DI161" s="24" t="n"/>
+      <c r="DJ161" s="24" t="n"/>
+      <c r="DK161" s="24" t="n"/>
+      <c r="DL161" s="24" t="n"/>
+      <c r="DM161" s="24" t="n"/>
+      <c r="DN161" s="24" t="n"/>
+      <c r="DO161" s="24" t="n"/>
+      <c r="DP161" s="24" t="n"/>
+      <c r="DQ161" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4fb00b8396ed01ac9098b909076acca187018877e203df68a40b7905bbf60d46", "away_team": "Misa Esports", "event_id": "143813", "event_start_utc": "2026-10-08T16:00:00Z", "features": {"away_elo": 1724.212682, "away_history_count": 45, "home_elo": 1796.002978, "home_history_count": 115}, "historical_source_observation_times_verified": false, "home_team": "Fire Flux Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7097": 115, "bo3:2:9593": 45}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7097": "2026-08-28T16:30:00Z", "bo3:2:9593": "2026-10-03T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.1143685463659617, "platt_slope": 0.7683784881494086, "ratings": {"bo3:2:7097": 1796.002978, "bo3:2:9593": 1724.212682}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T22:27:21.612006+00:00", "team_ids": ["bo3:2:7097", "bo3:2:9593"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-07T22:27:21.612006+00:00", "probabilities": {"away": 0.477383, "home": 0.522617}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "61e2237c3d364936da93fe65b1707c0322e0e2d94b272e5af1ff32f31652df53", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="36" customHeight="1">
+      <c r="A162" s="24" t="inlineStr">
+        <is>
+          <t>abfb041f0ca64ef5</t>
+        </is>
+      </c>
+      <c r="B162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D162" s="24" t="inlineStr">
+        <is>
+          <t>152663</t>
+        </is>
+      </c>
+      <c r="E162" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F162" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="G162" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I162" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J162" s="25" t="n"/>
+      <c r="K162" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L162" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M162" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N162" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O162" s="28" t="n">
+        <v>0.605665</v>
+      </c>
+      <c r="P162" s="28" t="n"/>
+      <c r="Q162" s="28" t="n">
+        <v>0.03485</v>
+      </c>
+      <c r="R162" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="S162" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T162" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U162" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V162" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W162" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y162" s="25" t="n"/>
+      <c r="Z162" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA162" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB162" s="28" t="n">
+        <v>-0.010815</v>
+      </c>
+      <c r="AC162" s="30" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AD162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:03:43.005367Z</t>
+        </is>
+      </c>
+      <c r="AE162" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-100t-nrg-2026-10-11).</t>
+        </is>
+      </c>
+      <c r="AF162" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG162" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH162" s="24" t="n"/>
+      <c r="AI162" s="31" t="n"/>
+      <c r="AJ162" s="31" t="n"/>
+      <c r="AK162" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL162" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM162" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN162" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO162" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP162" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AQ162" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AR162" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AS162" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT162" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU162" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV162" s="24" t="n"/>
+      <c r="AW162" s="24" t="n"/>
+      <c r="AX162" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY162" s="24" t="n"/>
+      <c r="AZ162" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA162" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB162" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC162" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD162" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE162" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF162" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG162" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:19.191912Z</t>
+        </is>
+      </c>
+      <c r="BI162" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ162" s="25" t="n"/>
+      <c r="BK162" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL162" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM162" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN162" s="28" t="n"/>
+      <c r="BO162" s="28" t="n"/>
+      <c r="BP162" s="25" t="n"/>
+      <c r="BQ162" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR162" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BS162" s="28" t="n"/>
+      <c r="BT162" s="28" t="n"/>
+      <c r="BU162" s="25" t="n"/>
+      <c r="BV162" s="29" t="n"/>
+      <c r="BW162" s="24" t="n"/>
+      <c r="BX162" s="30" t="n"/>
+      <c r="BY162" s="27" t="n"/>
+      <c r="BZ162" s="24" t="n"/>
+      <c r="CA162" s="31" t="n"/>
+      <c r="CB162" s="24" t="n"/>
+      <c r="CC162" s="24" t="n"/>
+      <c r="CD162" s="24" t="n"/>
+      <c r="CE162" s="24" t="n"/>
+      <c r="CF162" s="24" t="n"/>
+      <c r="CG162" s="24" t="n"/>
+      <c r="CH162" s="24" t="n"/>
+      <c r="CI162" s="24" t="n"/>
+      <c r="CJ162" s="24" t="n"/>
+      <c r="CK162" s="24" t="n"/>
+      <c r="CL162" s="24" t="n"/>
+      <c r="CM162" s="24" t="n"/>
+      <c r="CN162" s="24" t="n"/>
+      <c r="CO162" s="24" t="n"/>
+      <c r="CP162" s="24" t="n"/>
+      <c r="CQ162" s="24" t="n"/>
+      <c r="CR162" s="24" t="n"/>
+      <c r="CS162" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT162" s="24" t="n"/>
+      <c r="CU162" s="24" t="n"/>
+      <c r="CV162" s="24" t="n"/>
+      <c r="CW162" s="24" t="n"/>
+      <c r="CX162" s="24" t="n"/>
+      <c r="CY162" s="24" t="n"/>
+      <c r="CZ162" s="24" t="n"/>
+      <c r="DA162" s="24" t="n"/>
+      <c r="DB162" s="24" t="n"/>
+      <c r="DC162" s="24" t="n"/>
+      <c r="DD162" s="24" t="n"/>
+      <c r="DE162" s="24" t="n"/>
+      <c r="DF162" s="24" t="n"/>
+      <c r="DG162" s="24" t="n"/>
+      <c r="DH162" s="24" t="n"/>
+      <c r="DI162" s="24" t="n"/>
+      <c r="DJ162" s="24" t="n"/>
+      <c r="DK162" s="24" t="n"/>
+      <c r="DL162" s="24" t="n"/>
+      <c r="DM162" s="24" t="n"/>
+      <c r="DN162" s="24" t="n"/>
+      <c r="DO162" s="24" t="n"/>
+      <c r="DP162" s="24" t="n"/>
+      <c r="DQ162" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69", "away_team": "NRG", "event_id": "152663", "event_start_utc": "2026-10-11T09:00:00Z", "features": {"away_elo": 1983.731977, "away_history_count": 134, "home_elo": 2077.000538, "home_history_count": 113}, "historical_source_observation_times_verified": false, "home_team": "100 Thieves", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7298": 113, "bo3:2:7347": 134}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7298": "2026-10-09T12:20:00Z", "bo3:2:7347": "2026-10-10T09:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11616902206451739, "platt_slope": 0.770524736739285, "ratings": {"bo3:2:7298": 2077.000538, "bo3:2:7347": 1983.731977}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-11T07:25:19.097996+00:00", "team_ids": ["bo3:2:7298", "bo3:2:7347"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-11T07:25:19.097996+00:00", "probabilities": {"away": 0.394335, "home": 0.605665}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "7d2a5cfa57e4eed769fadffb96a90da6462335220fc9113ed5a59c45fb991406", "sport": "VALORANT"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="36" customHeight="1">
+      <c r="A163" s="24" t="inlineStr">
+        <is>
+          <t>560b09b740ce4b8b</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>152663</t>
+        </is>
+      </c>
+      <c r="E163" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H163" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I163" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J163" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K163" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L163" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M163" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N163" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O163" s="28" t="n">
+        <v>0.510059</v>
+      </c>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="28" t="n">
+        <v>-0.020457</v>
+      </c>
+      <c r="R163" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S163" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T163" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U163" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V163" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W163" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y163" s="25" t="n"/>
+      <c r="Z163" s="26" t="n"/>
+      <c r="AA163" s="28" t="n"/>
+      <c r="AB163" s="28" t="n"/>
+      <c r="AC163" s="30" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="AD163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:03:45.745269Z</t>
+        </is>
+      </c>
+      <c r="AE163" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=tsc-valorant-100t-nrg-2026-10-11-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF163" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG163" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH163" s="24" t="n"/>
+      <c r="AI163" s="31" t="n"/>
+      <c r="AJ163" s="31" t="n"/>
+      <c r="AK163" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL163" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM163" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN163" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO163" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP163" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AQ163" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AR163" s="24" t="inlineStr">
+        <is>
+          <t>NRG</t>
+        </is>
+      </c>
+      <c r="AS163" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT163" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU163" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV163" s="24" t="n"/>
+      <c r="AW163" s="24" t="n"/>
+      <c r="AX163" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY163" s="24" t="n"/>
+      <c r="AZ163" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA163" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB163" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC163" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD163" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG163" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:25:29.314396Z</t>
+        </is>
+      </c>
+      <c r="BI163" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ163" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK163" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL163" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM163" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN163" s="28" t="n"/>
+      <c r="BO163" s="28" t="n"/>
+      <c r="BP163" s="25" t="n"/>
+      <c r="BQ163" s="27" t="n"/>
+      <c r="BR163" s="28" t="n"/>
+      <c r="BS163" s="28" t="n"/>
+      <c r="BT163" s="28" t="n"/>
+      <c r="BU163" s="25" t="n"/>
+      <c r="BV163" s="29" t="n"/>
+      <c r="BW163" s="24" t="n"/>
+      <c r="BX163" s="30" t="n"/>
+      <c r="BY163" s="27" t="n"/>
+      <c r="BZ163" s="24" t="n"/>
+      <c r="CA163" s="31" t="n"/>
+      <c r="CB163" s="24" t="n"/>
+      <c r="CC163" s="24" t="n"/>
+      <c r="CD163" s="24" t="n"/>
+      <c r="CE163" s="24" t="n"/>
+      <c r="CF163" s="24" t="n"/>
+      <c r="CG163" s="24" t="n"/>
+      <c r="CH163" s="24" t="n"/>
+      <c r="CI163" s="24" t="n"/>
+      <c r="CJ163" s="24" t="n"/>
+      <c r="CK163" s="24" t="n"/>
+      <c r="CL163" s="24" t="n"/>
+      <c r="CM163" s="24" t="n"/>
+      <c r="CN163" s="24" t="n"/>
+      <c r="CO163" s="24" t="n"/>
+      <c r="CP163" s="24" t="n"/>
+      <c r="CQ163" s="24" t="n"/>
+      <c r="CR163" s="24" t="n"/>
+      <c r="CS163" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT163" s="24" t="n"/>
+      <c r="CU163" s="24" t="n"/>
+      <c r="CV163" s="24" t="n"/>
+      <c r="CW163" s="24" t="n"/>
+      <c r="CX163" s="24" t="n"/>
+      <c r="CY163" s="24" t="n"/>
+      <c r="CZ163" s="24" t="n"/>
+      <c r="DA163" s="24" t="n"/>
+      <c r="DB163" s="24" t="n"/>
+      <c r="DC163" s="24" t="n"/>
+      <c r="DD163" s="24" t="n"/>
+      <c r="DE163" s="24" t="n"/>
+      <c r="DF163" s="24" t="n"/>
+      <c r="DG163" s="24" t="n"/>
+      <c r="DH163" s="24" t="n"/>
+      <c r="DI163" s="24" t="n"/>
+      <c r="DJ163" s="24" t="n"/>
+      <c r="DK163" s="24" t="n"/>
+      <c r="DL163" s="24" t="n"/>
+      <c r="DM163" s="24" t="n"/>
+      <c r="DN163" s="24" t="n"/>
+      <c r="DO163" s="24" t="n"/>
+      <c r="DP163" s="24" t="n"/>
+      <c r="DQ163" s="24" t="n"/>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="A164" s="24" t="inlineStr">
+        <is>
+          <t>1c652b5488014158</t>
+        </is>
+      </c>
+      <c r="B164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>152776</t>
+        </is>
+      </c>
+      <c r="E164" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="G164" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="I164" s="24" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J164" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K164" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L164" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M164" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N164" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O164" s="28" t="n">
+        <v>0.500179</v>
+      </c>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="28" t="n">
+        <v>-0.059292</v>
+      </c>
+      <c r="R164" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T164" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U164" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V164" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W164" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X164" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y164" s="25" t="n"/>
+      <c r="Z164" s="26" t="n"/>
+      <c r="AA164" s="28" t="n"/>
+      <c r="AB164" s="28" t="n"/>
+      <c r="AC164" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:03:47.008538Z</t>
+        </is>
+      </c>
+      <c r="AE164" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=tsc-valorant-t1-g2-2026-10-11-tot-2pt5).</t>
+        </is>
+      </c>
+      <c r="AF164" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG164" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH164" s="24" t="n"/>
+      <c r="AI164" s="31" t="n"/>
+      <c r="AJ164" s="31" t="n"/>
+      <c r="AK164" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL164" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM164" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN164" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO164" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP164" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AQ164" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AR164" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AS164" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT164" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU164" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV164" s="24" t="n"/>
+      <c r="AW164" s="24" t="n"/>
+      <c r="AX164" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY164" s="24" t="n"/>
+      <c r="AZ164" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA164" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB164" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC164" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD164" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG164" s="24" t="inlineStr">
+        <is>
+          <t>valorant-total-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:11.838532Z</t>
+        </is>
+      </c>
+      <c r="BI164" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ164" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BK164" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL164" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM164" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN164" s="28" t="n"/>
+      <c r="BO164" s="28" t="n"/>
+      <c r="BP164" s="25" t="n"/>
+      <c r="BQ164" s="27" t="n"/>
+      <c r="BR164" s="28" t="n"/>
+      <c r="BS164" s="28" t="n"/>
+      <c r="BT164" s="28" t="n"/>
+      <c r="BU164" s="25" t="n"/>
+      <c r="BV164" s="29" t="n"/>
+      <c r="BW164" s="24" t="n"/>
+      <c r="BX164" s="30" t="n"/>
+      <c r="BY164" s="27" t="n"/>
+      <c r="BZ164" s="24" t="n"/>
+      <c r="CA164" s="31" t="n"/>
+      <c r="CB164" s="24" t="n"/>
+      <c r="CC164" s="24" t="n"/>
+      <c r="CD164" s="24" t="n"/>
+      <c r="CE164" s="24" t="n"/>
+      <c r="CF164" s="24" t="n"/>
+      <c r="CG164" s="24" t="n"/>
+      <c r="CH164" s="24" t="n"/>
+      <c r="CI164" s="24" t="n"/>
+      <c r="CJ164" s="24" t="n"/>
+      <c r="CK164" s="24" t="n"/>
+      <c r="CL164" s="24" t="n"/>
+      <c r="CM164" s="24" t="n"/>
+      <c r="CN164" s="24" t="n"/>
+      <c r="CO164" s="24" t="n"/>
+      <c r="CP164" s="24" t="n"/>
+      <c r="CQ164" s="24" t="n"/>
+      <c r="CR164" s="24" t="n"/>
+      <c r="CS164" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT164" s="24" t="n"/>
+      <c r="CU164" s="24" t="n"/>
+      <c r="CV164" s="24" t="n"/>
+      <c r="CW164" s="24" t="n"/>
+      <c r="CX164" s="24" t="n"/>
+      <c r="CY164" s="24" t="n"/>
+      <c r="CZ164" s="24" t="n"/>
+      <c r="DA164" s="24" t="n"/>
+      <c r="DB164" s="24" t="n"/>
+      <c r="DC164" s="24" t="n"/>
+      <c r="DD164" s="24" t="n"/>
+      <c r="DE164" s="24" t="n"/>
+      <c r="DF164" s="24" t="n"/>
+      <c r="DG164" s="24" t="n"/>
+      <c r="DH164" s="24" t="n"/>
+      <c r="DI164" s="24" t="n"/>
+      <c r="DJ164" s="24" t="n"/>
+      <c r="DK164" s="24" t="n"/>
+      <c r="DL164" s="24" t="n"/>
+      <c r="DM164" s="24" t="n"/>
+      <c r="DN164" s="24" t="n"/>
+      <c r="DO164" s="24" t="n"/>
+      <c r="DP164" s="24" t="n"/>
+      <c r="DQ164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="24" t="inlineStr">
+        <is>
+          <t>c4f250cc64a64efe</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:54.158997Z</t>
+        </is>
+      </c>
+      <c r="C165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D165" s="24" t="inlineStr">
+        <is>
+          <t>152776</t>
+        </is>
+      </c>
+      <c r="E165" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F165" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="H165" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I165" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J165" s="25" t="n"/>
+      <c r="K165" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L165" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M165" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N165" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O165" s="28" t="n">
+        <v>0.514196</v>
+      </c>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="28" t="n">
+        <v>0.123571</v>
+      </c>
+      <c r="R165" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S165" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T165" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U165" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V165" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W165" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X165" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="25" t="n"/>
+      <c r="Z165" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="AA165" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AB165" s="28" t="n">
+        <v>-0.000625</v>
+      </c>
+      <c r="AC165" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T16:03:48.300822Z</t>
+        </is>
+      </c>
+      <c r="AE165" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-t1-g2-2026-10-11).</t>
+        </is>
+      </c>
+      <c r="AF165" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG165" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH165" s="24" t="n"/>
+      <c r="AI165" s="31" t="n"/>
+      <c r="AJ165" s="31" t="n"/>
+      <c r="AK165" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL165" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM165" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN165" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO165" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP165" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AQ165" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AR165" s="24" t="inlineStr">
+        <is>
+          <t>G2 Esports</t>
+        </is>
+      </c>
+      <c r="AS165" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AT165" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AU165" s="24" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="AV165" s="24" t="n"/>
+      <c r="AW165" s="24" t="n"/>
+      <c r="AX165" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY165" s="24" t="n"/>
+      <c r="AZ165" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA165" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BB165" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC165" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD165" s="24" t="inlineStr">
+        <is>
+          <t>13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69</t>
+        </is>
+      </c>
+      <c r="BE165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG165" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T07:27:21.974126Z</t>
+        </is>
+      </c>
+      <c r="BI165" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ165" s="25" t="n"/>
+      <c r="BK165" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL165" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM165" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN165" s="28" t="n"/>
+      <c r="BO165" s="28" t="n"/>
+      <c r="BP165" s="25" t="n"/>
+      <c r="BQ165" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BR165" s="28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BS165" s="28" t="n"/>
+      <c r="BT165" s="28" t="n"/>
+      <c r="BU165" s="25" t="n"/>
+      <c r="BV165" s="29" t="n"/>
+      <c r="BW165" s="24" t="n"/>
+      <c r="BX165" s="30" t="n"/>
+      <c r="BY165" s="27" t="n"/>
+      <c r="BZ165" s="24" t="n"/>
+      <c r="CA165" s="31" t="n"/>
+      <c r="CB165" s="24" t="n"/>
+      <c r="CC165" s="24" t="n"/>
+      <c r="CD165" s="24" t="n"/>
+      <c r="CE165" s="24" t="n"/>
+      <c r="CF165" s="24" t="n"/>
+      <c r="CG165" s="24" t="n"/>
+      <c r="CH165" s="24" t="n"/>
+      <c r="CI165" s="24" t="n"/>
+      <c r="CJ165" s="24" t="n"/>
+      <c r="CK165" s="24" t="n"/>
+      <c r="CL165" s="24" t="n"/>
+      <c r="CM165" s="24" t="n"/>
+      <c r="CN165" s="24" t="n"/>
+      <c r="CO165" s="24" t="n"/>
+      <c r="CP165" s="24" t="n"/>
+      <c r="CQ165" s="24" t="n"/>
+      <c r="CR165" s="24" t="n"/>
+      <c r="CS165" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT165" s="24" t="n"/>
+      <c r="CU165" s="24" t="n"/>
+      <c r="CV165" s="24" t="n"/>
+      <c r="CW165" s="24" t="n"/>
+      <c r="CX165" s="24" t="n"/>
+      <c r="CY165" s="24" t="n"/>
+      <c r="CZ165" s="24" t="n"/>
+      <c r="DA165" s="24" t="n"/>
+      <c r="DB165" s="24" t="n"/>
+      <c r="DC165" s="24" t="n"/>
+      <c r="DD165" s="24" t="n"/>
+      <c r="DE165" s="24" t="n"/>
+      <c r="DF165" s="24" t="n"/>
+      <c r="DG165" s="24" t="n"/>
+      <c r="DH165" s="24" t="n"/>
+      <c r="DI165" s="24" t="n"/>
+      <c r="DJ165" s="24" t="n"/>
+      <c r="DK165" s="24" t="n"/>
+      <c r="DL165" s="24" t="n"/>
+      <c r="DM165" s="24" t="n"/>
+      <c r="DN165" s="24" t="n"/>
+      <c r="DO165" s="24" t="n"/>
+      <c r="DP165" s="24" t="n"/>
+      <c r="DQ165" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "13167e59620ddef10ebfa0d7d26db74a15baccaf70ae2fbdc1a1fe7f57e95d69", "away_team": "G2 Esports", "event_id": "152776", "event_start_utc": "2026-10-11T12:00:00Z", "features": {"away_elo": 1909.110814, "away_history_count": 168, "home_elo": 1902.071006, "home_history_count": 139}, "historical_source_observation_times_verified": false, "home_team": "T1", "inference_inputs": {"book_state": {"games_played": {"bo3:2:7283": 139, "bo3:2:7323": 168}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 64.0, "last_match_utc": {"bo3:2:7283": "2026-10-09T09:00:00Z", "bo3:2:7323": "2026-10-10T12:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.11616902206451739, "platt_slope": 0.770524736739285, "ratings": {"bo3:2:7283": 1902.071006, "bo3:2:7323": 1909.110814}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-11T07:25:19.097996+00:00", "team_ids": ["bo3:2:7283", "bo3:2:7323"]}, "market_type": "moneyline", "model_version": "valorant-tiered-elo-v6", "observed_at_utc": "2026-10-11T07:25:19.097996+00:00", "probabilities": {"away": 0.485804, "home": 0.514196}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "12456a453c6b5fc9e98e1e810c65fcff9a22e6971ab0a9f9d03a32489d4ba668", "sport": "VALORANT"}</t>
         </is>
       </c>
     </row>
